--- a/AAII_Financials/Yearly/EXFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EXFY_YR_FIN.xlsx
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-2800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1051,7 +1051,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>160100</v>
+        <v>162900</v>
       </c>
       <c r="E17" s="3">
         <v>140100</v>
@@ -1093,7 +1093,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-18000</v>
+        <v>-20800</v>
       </c>
       <c r="E18" s="3">
         <v>-800</v>
@@ -1195,7 +1195,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-17300</v>
+        <v>-20100</v>
       </c>
       <c r="E21" s="3">
         <v>-1500</v>
